--- a/기초데이터/원본/기후데이터/5. 기후데이터 방위각.xlsx
+++ b/기초데이터/원본/기후데이터/5. 기후데이터 방위각.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\passive\Remodeling_SW\기초데이터\원본\기후데이터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6334DE84-F146-4CD3-B889-036378C08402}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C8E36E-DB91-4F9A-B3D3-3E40B40A3CA7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" tabRatio="839" xr2:uid="{B631F572-E47C-4706-930D-6073D79E0137}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="18">
   <si>
     <t>01</t>
   </si>
@@ -66,17 +66,23 @@
     <t>북</t>
   </si>
   <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>강릉</t>
-  </si>
-  <si>
     <t>지역코드</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>지역명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>종류</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우측</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>좌측</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -159,7 +165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -249,26 +255,6 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="1" tint="0.499984740745262"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="1" tint="0.499984740745262"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color theme="0" tint="-0.14996795556505021"/>
       </left>
       <right/>
@@ -333,7 +319,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -393,37 +379,33 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="177" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="177" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -740,15 +722,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB3C6D99-3E02-487D-848D-AD62BBFEFCDE}">
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
@@ -756,44 +738,47 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18">
-        <v>1</v>
-      </c>
-      <c r="F1" s="19">
+      <c r="E1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="16">
+        <v>1</v>
+      </c>
+      <c r="G1" s="17">
         <v>2</v>
       </c>
-      <c r="G1" s="19">
+      <c r="H1" s="17">
         <v>3</v>
       </c>
-      <c r="H1" s="19">
+      <c r="I1" s="17">
         <v>4</v>
       </c>
-      <c r="I1" s="19">
+      <c r="J1" s="17">
         <v>5</v>
       </c>
-      <c r="J1" s="19">
+      <c r="K1" s="17">
         <v>6</v>
       </c>
-      <c r="K1" s="19">
+      <c r="L1" s="17">
         <v>7</v>
       </c>
-      <c r="L1" s="19">
+      <c r="M1" s="17">
         <v>8</v>
       </c>
-      <c r="M1" s="19">
+      <c r="N1" s="17">
         <v>9</v>
       </c>
-      <c r="N1" s="19">
+      <c r="O1" s="17">
         <v>10</v>
       </c>
-      <c r="O1" s="19">
+      <c r="P1" s="17">
         <v>11</v>
       </c>
-      <c r="P1" s="20">
+      <c r="Q1" s="18">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -806,7 +791,9 @@
       <c r="D2" s="5">
         <v>0</v>
       </c>
-      <c r="E2" s="6"/>
+      <c r="E2" s="23" t="s">
+        <v>16</v>
+      </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -817,9 +804,10 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="21"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P2" s="6"/>
+      <c r="Q2" s="19"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -832,44 +820,47 @@
       <c r="D3" s="8">
         <v>30</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="9">
         <v>6</v>
       </c>
-      <c r="F3" s="9">
+      <c r="G3" s="9">
         <v>9</v>
       </c>
-      <c r="G3" s="9">
+      <c r="H3" s="9">
         <v>9.0698087569101471</v>
       </c>
-      <c r="H3" s="9">
+      <c r="I3" s="9">
         <v>19.826843359155149</v>
       </c>
-      <c r="I3" s="9">
+      <c r="J3" s="9">
         <v>30.78858579510694</v>
       </c>
-      <c r="J3" s="9">
+      <c r="K3" s="9">
         <v>55.245239606129935</v>
       </c>
-      <c r="K3" s="9">
+      <c r="L3" s="9">
         <v>36.356659085580631</v>
       </c>
-      <c r="L3" s="9">
+      <c r="M3" s="9">
         <v>31.589597608564212</v>
       </c>
-      <c r="M3" s="9">
+      <c r="N3" s="9">
         <v>15.554678624170798</v>
       </c>
-      <c r="N3" s="9">
+      <c r="O3" s="9">
         <v>9</v>
       </c>
-      <c r="O3" s="9">
+      <c r="P3" s="9">
         <v>5.9289084225573667</v>
       </c>
-      <c r="P3" s="22">
+      <c r="Q3" s="20">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -882,44 +873,47 @@
       <c r="D4" s="10">
         <v>45</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="9">
         <v>6</v>
       </c>
-      <c r="F4" s="9">
+      <c r="G4" s="9">
         <v>9</v>
       </c>
-      <c r="G4" s="9">
+      <c r="H4" s="9">
         <v>9.0698087569101471</v>
       </c>
-      <c r="H4" s="9">
+      <c r="I4" s="9">
         <v>19.826843359155149</v>
       </c>
-      <c r="I4" s="9">
+      <c r="J4" s="9">
         <v>30.78858579510694</v>
       </c>
-      <c r="J4" s="9">
+      <c r="K4" s="9">
         <v>55.245239606129935</v>
       </c>
-      <c r="K4" s="9">
+      <c r="L4" s="9">
         <v>36.356659085580631</v>
       </c>
-      <c r="L4" s="9">
+      <c r="M4" s="9">
         <v>31.589597608564212</v>
       </c>
-      <c r="M4" s="9">
+      <c r="N4" s="9">
         <v>15.554678624170798</v>
       </c>
-      <c r="N4" s="9">
+      <c r="O4" s="9">
         <v>9</v>
       </c>
-      <c r="O4" s="9">
+      <c r="P4" s="9">
         <v>5.9289084225573667</v>
       </c>
-      <c r="P4" s="22">
+      <c r="Q4" s="20">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -932,44 +926,47 @@
       <c r="D5" s="10">
         <v>60</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="9">
         <v>6</v>
       </c>
-      <c r="F5" s="9">
+      <c r="G5" s="9">
         <v>9</v>
       </c>
-      <c r="G5" s="9">
+      <c r="H5" s="9">
         <v>9.0698087569101471</v>
       </c>
-      <c r="H5" s="9">
+      <c r="I5" s="9">
         <v>19.826843359155149</v>
       </c>
-      <c r="I5" s="9">
+      <c r="J5" s="9">
         <v>30.78858579510694</v>
       </c>
-      <c r="J5" s="9">
+      <c r="K5" s="9">
         <v>55.245239606129935</v>
       </c>
-      <c r="K5" s="9">
+      <c r="L5" s="9">
         <v>36.356659085580631</v>
       </c>
-      <c r="L5" s="9">
+      <c r="M5" s="9">
         <v>31.589597608564212</v>
       </c>
-      <c r="M5" s="9">
+      <c r="N5" s="9">
         <v>15.554678624170798</v>
       </c>
-      <c r="N5" s="9">
+      <c r="O5" s="9">
         <v>9</v>
       </c>
-      <c r="O5" s="9">
+      <c r="P5" s="9">
         <v>5.9289084225573667</v>
       </c>
-      <c r="P5" s="22">
+      <c r="Q5" s="20">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -982,44 +979,47 @@
       <c r="D6" s="11">
         <v>90</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="9">
         <v>6</v>
       </c>
-      <c r="F6" s="9">
+      <c r="G6" s="9">
         <v>9</v>
       </c>
-      <c r="G6" s="9">
+      <c r="H6" s="9">
         <v>9.0698087569101471</v>
       </c>
-      <c r="H6" s="9">
+      <c r="I6" s="9">
         <v>19.826843359155149</v>
       </c>
-      <c r="I6" s="9">
+      <c r="J6" s="9">
         <v>30.78858579510694</v>
       </c>
-      <c r="J6" s="9">
+      <c r="K6" s="9">
         <v>55.245239606129935</v>
       </c>
-      <c r="K6" s="9">
+      <c r="L6" s="9">
         <v>36.356659085580631</v>
       </c>
-      <c r="L6" s="9">
+      <c r="M6" s="9">
         <v>31.589597608564212</v>
       </c>
-      <c r="M6" s="9">
+      <c r="N6" s="9">
         <v>15.554678624170798</v>
       </c>
-      <c r="N6" s="9">
+      <c r="O6" s="9">
         <v>9</v>
       </c>
-      <c r="O6" s="9">
+      <c r="P6" s="9">
         <v>5.9289084225573667</v>
       </c>
-      <c r="P6" s="22">
+      <c r="Q6" s="20">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1032,44 +1032,47 @@
       <c r="D7" s="10">
         <v>30</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="13">
         <v>8</v>
       </c>
-      <c r="F7" s="13">
+      <c r="G7" s="13">
         <v>9.797439009740641</v>
       </c>
-      <c r="G7" s="13">
+      <c r="H7" s="13">
         <v>10.374786255459002</v>
       </c>
-      <c r="H7" s="13">
+      <c r="I7" s="13">
         <v>19.623088765134398</v>
       </c>
-      <c r="I7" s="13">
+      <c r="J7" s="13">
         <v>29.244273154410187</v>
       </c>
-      <c r="J7" s="13">
+      <c r="K7" s="13">
         <v>50.474526655788154</v>
       </c>
-      <c r="K7" s="13">
+      <c r="L7" s="13">
         <v>33.619523617959302</v>
       </c>
-      <c r="L7" s="13">
+      <c r="M7" s="13">
         <v>29.760635923183425</v>
       </c>
-      <c r="M7" s="13">
+      <c r="N7" s="13">
         <v>16.302931377827765</v>
       </c>
-      <c r="N7" s="13">
+      <c r="O7" s="13">
         <v>11</v>
       </c>
-      <c r="O7" s="13">
+      <c r="P7" s="13">
         <v>7.0874536205430729</v>
       </c>
-      <c r="P7" s="23">
+      <c r="Q7" s="21">
         <v>5.1404518978219995</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -1082,44 +1085,47 @@
       <c r="D8" s="10">
         <v>45</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="13">
         <v>8</v>
       </c>
-      <c r="F8" s="13">
+      <c r="G8" s="13">
         <v>9.797439009740641</v>
       </c>
-      <c r="G8" s="13">
+      <c r="H8" s="13">
         <v>10.374786255459002</v>
       </c>
-      <c r="H8" s="13">
+      <c r="I8" s="13">
         <v>19.623088765134398</v>
       </c>
-      <c r="I8" s="13">
+      <c r="J8" s="13">
         <v>29.244273154410187</v>
       </c>
-      <c r="J8" s="13">
+      <c r="K8" s="13">
         <v>50.474526655788154</v>
       </c>
-      <c r="K8" s="13">
+      <c r="L8" s="13">
         <v>33.619523617959302</v>
       </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
         <v>29.760635923183425</v>
       </c>
-      <c r="M8" s="13">
+      <c r="N8" s="13">
         <v>16.302931377827765</v>
       </c>
-      <c r="N8" s="13">
+      <c r="O8" s="13">
         <v>11</v>
       </c>
-      <c r="O8" s="13">
+      <c r="P8" s="13">
         <v>7.0874536205430729</v>
       </c>
-      <c r="P8" s="23">
+      <c r="Q8" s="21">
         <v>5.1404518978219995</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1132,44 +1138,47 @@
       <c r="D9" s="10">
         <v>60</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="13">
         <v>8</v>
       </c>
-      <c r="F9" s="13">
+      <c r="G9" s="13">
         <v>9.797439009740641</v>
       </c>
-      <c r="G9" s="13">
+      <c r="H9" s="13">
         <v>10.374786255459002</v>
       </c>
-      <c r="H9" s="13">
+      <c r="I9" s="13">
         <v>19.623088765134398</v>
       </c>
-      <c r="I9" s="13">
+      <c r="J9" s="13">
         <v>29.244273154410187</v>
       </c>
-      <c r="J9" s="13">
+      <c r="K9" s="13">
         <v>50.474526655788154</v>
       </c>
-      <c r="K9" s="13">
+      <c r="L9" s="13">
         <v>33.619523617959302</v>
       </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
         <v>29.760635923183425</v>
       </c>
-      <c r="M9" s="13">
+      <c r="N9" s="13">
         <v>16.302931377827765</v>
       </c>
-      <c r="N9" s="13">
+      <c r="O9" s="13">
         <v>11</v>
       </c>
-      <c r="O9" s="13">
+      <c r="P9" s="13">
         <v>7.0874536205430729</v>
       </c>
-      <c r="P9" s="23">
+      <c r="Q9" s="21">
         <v>5.1404518978219995</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1182,44 +1191,47 @@
       <c r="D10" s="10">
         <v>90</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="13">
         <v>8</v>
       </c>
-      <c r="F10" s="13">
+      <c r="G10" s="13">
         <v>9.797439009740641</v>
       </c>
-      <c r="G10" s="13">
+      <c r="H10" s="13">
         <v>10.374786255459002</v>
       </c>
-      <c r="H10" s="13">
+      <c r="I10" s="13">
         <v>19.623088765134398</v>
       </c>
-      <c r="I10" s="13">
+      <c r="J10" s="13">
         <v>29.244273154410187</v>
       </c>
-      <c r="J10" s="13">
+      <c r="K10" s="13">
         <v>50.474526655788154</v>
       </c>
-      <c r="K10" s="13">
+      <c r="L10" s="13">
         <v>33.619523617959302</v>
       </c>
-      <c r="L10" s="13">
+      <c r="M10" s="13">
         <v>29.760635923183425</v>
       </c>
-      <c r="M10" s="13">
+      <c r="N10" s="13">
         <v>16.302931377827765</v>
       </c>
-      <c r="N10" s="13">
+      <c r="O10" s="13">
         <v>11</v>
       </c>
-      <c r="O10" s="13">
+      <c r="P10" s="13">
         <v>7.0874536205430729</v>
       </c>
-      <c r="P10" s="23">
+      <c r="Q10" s="21">
         <v>5.1404518978219995</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1232,44 +1244,47 @@
       <c r="D11" s="8">
         <v>30</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="9">
         <v>3</v>
       </c>
-      <c r="F11" s="9">
+      <c r="G11" s="9">
         <v>1.3640431730263698</v>
       </c>
-      <c r="G11" s="9">
+      <c r="H11" s="9">
         <v>5</v>
       </c>
-      <c r="H11" s="9">
+      <c r="I11" s="9">
         <v>15.758759275137187</v>
       </c>
-      <c r="I11" s="9">
+      <c r="J11" s="9">
         <v>28.545285741720296</v>
       </c>
-      <c r="J11" s="9">
+      <c r="K11" s="9">
         <v>54.979860232952127</v>
       </c>
-      <c r="K11" s="9">
+      <c r="L11" s="9">
         <v>35.304004339491556</v>
       </c>
-      <c r="L11" s="9">
+      <c r="M11" s="9">
         <v>29.035211118062524</v>
       </c>
-      <c r="M11" s="9">
+      <c r="N11" s="9">
         <v>10.080888752871024</v>
       </c>
-      <c r="N11" s="9">
+      <c r="O11" s="9">
         <v>1.3797625974448828</v>
       </c>
-      <c r="O11" s="9">
+      <c r="P11" s="9">
         <v>3</v>
       </c>
-      <c r="P11" s="22">
+      <c r="Q11" s="20">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -1282,44 +1297,47 @@
       <c r="D12" s="10">
         <v>45</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="9">
         <v>3</v>
       </c>
-      <c r="F12" s="9">
+      <c r="G12" s="9">
         <v>1.3640431730263698</v>
       </c>
-      <c r="G12" s="9">
+      <c r="H12" s="9">
         <v>5</v>
       </c>
-      <c r="H12" s="9">
+      <c r="I12" s="9">
         <v>15.758759275137187</v>
       </c>
-      <c r="I12" s="9">
+      <c r="J12" s="9">
         <v>28.545285741720296</v>
       </c>
-      <c r="J12" s="9">
+      <c r="K12" s="9">
         <v>54.979860232952127</v>
       </c>
-      <c r="K12" s="9">
+      <c r="L12" s="9">
         <v>35.304004339491556</v>
       </c>
-      <c r="L12" s="9">
+      <c r="M12" s="9">
         <v>29.035211118062524</v>
       </c>
-      <c r="M12" s="9">
+      <c r="N12" s="9">
         <v>10.080888752871024</v>
       </c>
-      <c r="N12" s="9">
+      <c r="O12" s="9">
         <v>1.3797625974448828</v>
       </c>
-      <c r="O12" s="9">
+      <c r="P12" s="9">
         <v>3</v>
       </c>
-      <c r="P12" s="22">
+      <c r="Q12" s="20">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -1332,44 +1350,47 @@
       <c r="D13" s="10">
         <v>60</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="9">
         <v>3</v>
       </c>
-      <c r="F13" s="9">
+      <c r="G13" s="9">
         <v>1.3640431730263698</v>
       </c>
-      <c r="G13" s="9">
+      <c r="H13" s="9">
         <v>5</v>
       </c>
-      <c r="H13" s="9">
+      <c r="I13" s="9">
         <v>15.758759275137187</v>
       </c>
-      <c r="I13" s="9">
+      <c r="J13" s="9">
         <v>28.545285741720296</v>
       </c>
-      <c r="J13" s="9">
+      <c r="K13" s="9">
         <v>54.979860232952127</v>
       </c>
-      <c r="K13" s="9">
+      <c r="L13" s="9">
         <v>35.304004339491556</v>
       </c>
-      <c r="L13" s="9">
+      <c r="M13" s="9">
         <v>29.035211118062524</v>
       </c>
-      <c r="M13" s="9">
+      <c r="N13" s="9">
         <v>10.080888752871024</v>
       </c>
-      <c r="N13" s="9">
+      <c r="O13" s="9">
         <v>1.3797625974448828</v>
       </c>
-      <c r="O13" s="9">
+      <c r="P13" s="9">
         <v>3</v>
       </c>
-      <c r="P13" s="22">
+      <c r="Q13" s="20">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -1382,44 +1403,47 @@
       <c r="D14" s="11">
         <v>90</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="9">
         <v>3</v>
       </c>
-      <c r="F14" s="9">
+      <c r="G14" s="9">
         <v>1.3640431730263698</v>
       </c>
-      <c r="G14" s="9">
+      <c r="H14" s="9">
         <v>5</v>
       </c>
-      <c r="H14" s="9">
+      <c r="I14" s="9">
         <v>15.758759275137187</v>
       </c>
-      <c r="I14" s="9">
+      <c r="J14" s="9">
         <v>28.545285741720296</v>
       </c>
-      <c r="J14" s="9">
+      <c r="K14" s="9">
         <v>54.979860232952127</v>
       </c>
-      <c r="K14" s="9">
+      <c r="L14" s="9">
         <v>35.304004339491556</v>
       </c>
-      <c r="L14" s="9">
+      <c r="M14" s="9">
         <v>29.035211118062524</v>
       </c>
-      <c r="M14" s="9">
+      <c r="N14" s="9">
         <v>10.080888752871024</v>
       </c>
-      <c r="N14" s="9">
+      <c r="O14" s="9">
         <v>1.3797625974448828</v>
       </c>
-      <c r="O14" s="9">
+      <c r="P14" s="9">
         <v>3</v>
       </c>
-      <c r="P14" s="22">
+      <c r="Q14" s="20">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1432,44 +1456,47 @@
       <c r="D15" s="10">
         <v>30</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="13">
         <v>3.8241316092900566</v>
       </c>
-      <c r="F15" s="13">
+      <c r="G15" s="13">
         <v>6.9685918546536847</v>
       </c>
-      <c r="G15" s="13">
+      <c r="H15" s="13">
         <v>7.31772525179327</v>
       </c>
-      <c r="H15" s="13">
+      <c r="I15" s="13">
         <v>16.033278110330148</v>
       </c>
-      <c r="I15" s="13">
+      <c r="J15" s="13">
         <v>25.735803678780343</v>
       </c>
-      <c r="J15" s="13">
+      <c r="K15" s="13">
         <v>45.738242191960886</v>
       </c>
-      <c r="K15" s="13">
+      <c r="L15" s="13">
         <v>29.591620584512551</v>
       </c>
-      <c r="L15" s="13">
+      <c r="M15" s="13">
         <v>25.248596457970017</v>
       </c>
-      <c r="M15" s="13">
+      <c r="N15" s="13">
         <v>12.950325778318421</v>
       </c>
-      <c r="N15" s="13">
+      <c r="O15" s="13">
         <v>6.6795491217764358</v>
       </c>
-      <c r="O15" s="13">
+      <c r="P15" s="13">
         <v>4.932892680868874</v>
       </c>
-      <c r="P15" s="23">
+      <c r="Q15" s="21">
         <v>3.1140640397079786</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1482,44 +1509,47 @@
       <c r="D16" s="10">
         <v>45</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="13">
         <v>3.8241316092900566</v>
       </c>
-      <c r="F16" s="13">
+      <c r="G16" s="13">
         <v>6.9685918546536847</v>
       </c>
-      <c r="G16" s="13">
+      <c r="H16" s="13">
         <v>7.31772525179327</v>
       </c>
-      <c r="H16" s="13">
+      <c r="I16" s="13">
         <v>16.033278110330148</v>
       </c>
-      <c r="I16" s="13">
+      <c r="J16" s="13">
         <v>25.735803678780343</v>
       </c>
-      <c r="J16" s="13">
+      <c r="K16" s="13">
         <v>45.738242191960886</v>
       </c>
-      <c r="K16" s="13">
+      <c r="L16" s="13">
         <v>29.591620584512551</v>
       </c>
-      <c r="L16" s="13">
+      <c r="M16" s="13">
         <v>25.248596457970017</v>
       </c>
-      <c r="M16" s="13">
+      <c r="N16" s="13">
         <v>12.950325778318421</v>
       </c>
-      <c r="N16" s="13">
+      <c r="O16" s="13">
         <v>6.6795491217764358</v>
       </c>
-      <c r="O16" s="13">
+      <c r="P16" s="13">
         <v>4.932892680868874</v>
       </c>
-      <c r="P16" s="23">
+      <c r="Q16" s="21">
         <v>3.1140640397079786</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -1532,44 +1562,47 @@
       <c r="D17" s="10">
         <v>60</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="13">
         <v>3.8241316092900566</v>
       </c>
-      <c r="F17" s="13">
+      <c r="G17" s="13">
         <v>6.9685918546536847</v>
       </c>
-      <c r="G17" s="13">
+      <c r="H17" s="13">
         <v>7.31772525179327</v>
       </c>
-      <c r="H17" s="13">
+      <c r="I17" s="13">
         <v>16.033278110330148</v>
       </c>
-      <c r="I17" s="13">
+      <c r="J17" s="13">
         <v>25.735803678780343</v>
       </c>
-      <c r="J17" s="13">
+      <c r="K17" s="13">
         <v>45.738242191960886</v>
       </c>
-      <c r="K17" s="13">
+      <c r="L17" s="13">
         <v>29.591620584512551</v>
       </c>
-      <c r="L17" s="13">
+      <c r="M17" s="13">
         <v>25.248596457970017</v>
       </c>
-      <c r="M17" s="13">
+      <c r="N17" s="13">
         <v>12.950325778318421</v>
       </c>
-      <c r="N17" s="13">
+      <c r="O17" s="13">
         <v>6.6795491217764358</v>
       </c>
-      <c r="O17" s="13">
+      <c r="P17" s="13">
         <v>4.932892680868874</v>
       </c>
-      <c r="P17" s="23">
+      <c r="Q17" s="21">
         <v>3.1140640397079786</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1582,44 +1615,47 @@
       <c r="D18" s="10">
         <v>90</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="13">
         <v>3.8241316092900566</v>
       </c>
-      <c r="F18" s="13">
+      <c r="G18" s="13">
         <v>6.9685918546536847</v>
       </c>
-      <c r="G18" s="13">
+      <c r="H18" s="13">
         <v>7.31772525179327</v>
       </c>
-      <c r="H18" s="13">
+      <c r="I18" s="13">
         <v>16.033278110330148</v>
       </c>
-      <c r="I18" s="13">
+      <c r="J18" s="13">
         <v>25.735803678780343</v>
       </c>
-      <c r="J18" s="13">
+      <c r="K18" s="13">
         <v>45.738242191960886</v>
       </c>
-      <c r="K18" s="13">
+      <c r="L18" s="13">
         <v>29.591620584512551</v>
       </c>
-      <c r="L18" s="13">
+      <c r="M18" s="13">
         <v>25.248596457970017</v>
       </c>
-      <c r="M18" s="13">
+      <c r="N18" s="13">
         <v>12.950325778318421</v>
       </c>
-      <c r="N18" s="13">
+      <c r="O18" s="13">
         <v>6.6795491217764358</v>
       </c>
-      <c r="O18" s="13">
+      <c r="P18" s="13">
         <v>4.932892680868874</v>
       </c>
-      <c r="P18" s="23">
+      <c r="Q18" s="21">
         <v>3.1140640397079786</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -1632,44 +1668,47 @@
       <c r="D19" s="8">
         <v>30</v>
       </c>
-      <c r="E19" s="9">
-        <v>0</v>
+      <c r="E19" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="F19" s="9">
         <v>0</v>
       </c>
       <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
         <v>1.3560955547887117</v>
       </c>
-      <c r="H19" s="9">
+      <c r="I19" s="9">
         <v>12.512901561510191</v>
       </c>
-      <c r="I19" s="9">
+      <c r="J19" s="9">
         <v>23.73236728249196</v>
       </c>
-      <c r="J19" s="9">
+      <c r="K19" s="9">
         <v>49.148775584702634</v>
       </c>
-      <c r="K19" s="9">
+      <c r="L19" s="9">
         <v>31.316097414702618</v>
       </c>
-      <c r="L19" s="9">
+      <c r="M19" s="9">
         <v>24.266808894509548</v>
       </c>
-      <c r="M19" s="9">
+      <c r="N19" s="9">
         <v>6.9575517234331485</v>
       </c>
-      <c r="N19" s="9">
-        <v>0</v>
-      </c>
       <c r="O19" s="9">
         <v>0</v>
       </c>
-      <c r="P19" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P19" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -1682,44 +1721,47 @@
       <c r="D20" s="10">
         <v>45</v>
       </c>
-      <c r="E20" s="9">
-        <v>0</v>
+      <c r="E20" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="F20" s="9">
         <v>0</v>
       </c>
       <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
         <v>1.3560955547887117</v>
       </c>
-      <c r="H20" s="9">
+      <c r="I20" s="9">
         <v>12.512901561510191</v>
       </c>
-      <c r="I20" s="9">
+      <c r="J20" s="9">
         <v>23.73236728249196</v>
       </c>
-      <c r="J20" s="9">
+      <c r="K20" s="9">
         <v>49.148775584702634</v>
       </c>
-      <c r="K20" s="9">
+      <c r="L20" s="9">
         <v>31.316097414702618</v>
       </c>
-      <c r="L20" s="9">
+      <c r="M20" s="9">
         <v>24.266808894509548</v>
       </c>
-      <c r="M20" s="9">
+      <c r="N20" s="9">
         <v>6.9575517234331485</v>
       </c>
-      <c r="N20" s="9">
-        <v>0</v>
-      </c>
       <c r="O20" s="9">
         <v>0</v>
       </c>
-      <c r="P20" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P20" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
@@ -1732,44 +1774,47 @@
       <c r="D21" s="10">
         <v>60</v>
       </c>
-      <c r="E21" s="9">
-        <v>0</v>
+      <c r="E21" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="F21" s="9">
         <v>0</v>
       </c>
       <c r="G21" s="9">
+        <v>0</v>
+      </c>
+      <c r="H21" s="9">
         <v>1.3560955547887117</v>
       </c>
-      <c r="H21" s="9">
+      <c r="I21" s="9">
         <v>12.512901561510191</v>
       </c>
-      <c r="I21" s="9">
+      <c r="J21" s="9">
         <v>23.73236728249196</v>
       </c>
-      <c r="J21" s="9">
+      <c r="K21" s="9">
         <v>49.148775584702634</v>
       </c>
-      <c r="K21" s="9">
+      <c r="L21" s="9">
         <v>31.316097414702618</v>
       </c>
-      <c r="L21" s="9">
+      <c r="M21" s="9">
         <v>24.266808894509548</v>
       </c>
-      <c r="M21" s="9">
+      <c r="N21" s="9">
         <v>6.9575517234331485</v>
       </c>
-      <c r="N21" s="9">
-        <v>0</v>
-      </c>
       <c r="O21" s="9">
         <v>0</v>
       </c>
-      <c r="P21" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -1782,44 +1827,47 @@
       <c r="D22" s="11">
         <v>90</v>
       </c>
-      <c r="E22" s="9">
-        <v>0</v>
+      <c r="E22" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
         <v>1.3560955547887117</v>
       </c>
-      <c r="H22" s="9">
+      <c r="I22" s="9">
         <v>12.512901561510191</v>
       </c>
-      <c r="I22" s="9">
+      <c r="J22" s="9">
         <v>23.73236728249196</v>
       </c>
-      <c r="J22" s="9">
+      <c r="K22" s="9">
         <v>49.148775584702634</v>
       </c>
-      <c r="K22" s="9">
+      <c r="L22" s="9">
         <v>31.316097414702618</v>
       </c>
-      <c r="L22" s="9">
+      <c r="M22" s="9">
         <v>24.266808894509548</v>
       </c>
-      <c r="M22" s="9">
+      <c r="N22" s="9">
         <v>6.9575517234331485</v>
       </c>
-      <c r="N22" s="9">
-        <v>0</v>
-      </c>
       <c r="O22" s="9">
         <v>0</v>
       </c>
-      <c r="P22" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P22" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1832,8 +1880,8 @@
       <c r="D23" s="10">
         <v>30</v>
       </c>
-      <c r="E23" s="13">
-        <v>0</v>
+      <c r="E23" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="F23" s="13">
         <v>0</v>
@@ -1865,11 +1913,14 @@
       <c r="O23" s="13">
         <v>0</v>
       </c>
-      <c r="P23" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P23" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
@@ -1882,8 +1933,8 @@
       <c r="D24" s="10">
         <v>45</v>
       </c>
-      <c r="E24" s="13">
-        <v>0</v>
+      <c r="E24" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="F24" s="13">
         <v>0</v>
@@ -1915,11 +1966,14 @@
       <c r="O24" s="13">
         <v>0</v>
       </c>
-      <c r="P24" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P24" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -1932,8 +1986,8 @@
       <c r="D25" s="10">
         <v>60</v>
       </c>
-      <c r="E25" s="13">
-        <v>0</v>
+      <c r="E25" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="F25" s="13">
         <v>0</v>
@@ -1965,11 +2019,14 @@
       <c r="O25" s="13">
         <v>0</v>
       </c>
-      <c r="P25" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P25" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -1982,8 +2039,8 @@
       <c r="D26" s="10">
         <v>90</v>
       </c>
-      <c r="E26" s="13">
-        <v>0</v>
+      <c r="E26" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="F26" s="13">
         <v>0</v>
@@ -2015,11 +2072,14 @@
       <c r="O26" s="13">
         <v>0</v>
       </c>
-      <c r="P26" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P26" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -2032,44 +2092,47 @@
       <c r="D27" s="8">
         <v>30</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="9">
         <v>2.8095864818095313</v>
       </c>
-      <c r="F27" s="9">
+      <c r="G27" s="9">
         <v>5.3957827286710192</v>
       </c>
-      <c r="G27" s="9">
+      <c r="H27" s="9">
         <v>5.3503832384118741</v>
       </c>
-      <c r="H27" s="9">
+      <c r="I27" s="9">
         <v>13.344361598686229</v>
       </c>
-      <c r="I27" s="9">
+      <c r="J27" s="9">
         <v>22.923069610190264</v>
       </c>
-      <c r="J27" s="9">
+      <c r="K27" s="9">
         <v>41.961568091485923</v>
       </c>
-      <c r="K27" s="9">
+      <c r="L27" s="9">
         <v>26.467023145206021</v>
       </c>
-      <c r="L27" s="9">
+      <c r="M27" s="9">
         <v>21.79453973006644</v>
       </c>
-      <c r="M27" s="9">
+      <c r="N27" s="9">
         <v>10.467927838164099</v>
       </c>
-      <c r="N27" s="9">
+      <c r="O27" s="9">
         <v>4.9479627544026217</v>
       </c>
-      <c r="O27" s="9">
+      <c r="P27" s="9">
         <v>3.800222093309602</v>
       </c>
-      <c r="P27" s="22">
+      <c r="Q27" s="20">
         <v>2.1620575762215903</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
@@ -2082,44 +2145,47 @@
       <c r="D28" s="10">
         <v>45</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="9">
         <v>2.8095864818095313</v>
       </c>
-      <c r="F28" s="9">
+      <c r="G28" s="9">
         <v>5.3957827286710192</v>
       </c>
-      <c r="G28" s="9">
+      <c r="H28" s="9">
         <v>5.3503832384118741</v>
       </c>
-      <c r="H28" s="9">
+      <c r="I28" s="9">
         <v>13.344361598686229</v>
       </c>
-      <c r="I28" s="9">
+      <c r="J28" s="9">
         <v>22.923069610190264</v>
       </c>
-      <c r="J28" s="9">
+      <c r="K28" s="9">
         <v>41.961568091485923</v>
       </c>
-      <c r="K28" s="9">
+      <c r="L28" s="9">
         <v>26.467023145206021</v>
       </c>
-      <c r="L28" s="9">
+      <c r="M28" s="9">
         <v>21.79453973006644</v>
       </c>
-      <c r="M28" s="9">
+      <c r="N28" s="9">
         <v>10.467927838164099</v>
       </c>
-      <c r="N28" s="9">
+      <c r="O28" s="9">
         <v>4.9479627544026217</v>
       </c>
-      <c r="O28" s="9">
+      <c r="P28" s="9">
         <v>3.800222093309602</v>
       </c>
-      <c r="P28" s="22">
+      <c r="Q28" s="20">
         <v>2.1620575762215903</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -2132,44 +2198,47 @@
       <c r="D29" s="10">
         <v>60</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="9">
         <v>2.8095864818095313</v>
       </c>
-      <c r="F29" s="9">
+      <c r="G29" s="9">
         <v>5.3957827286710192</v>
       </c>
-      <c r="G29" s="9">
+      <c r="H29" s="9">
         <v>5.3503832384118741</v>
       </c>
-      <c r="H29" s="9">
+      <c r="I29" s="9">
         <v>13.344361598686229</v>
       </c>
-      <c r="I29" s="9">
+      <c r="J29" s="9">
         <v>22.923069610190264</v>
       </c>
-      <c r="J29" s="9">
+      <c r="K29" s="9">
         <v>41.961568091485923</v>
       </c>
-      <c r="K29" s="9">
+      <c r="L29" s="9">
         <v>26.467023145206021</v>
       </c>
-      <c r="L29" s="9">
+      <c r="M29" s="9">
         <v>21.79453973006644</v>
       </c>
-      <c r="M29" s="9">
+      <c r="N29" s="9">
         <v>10.467927838164099</v>
       </c>
-      <c r="N29" s="9">
+      <c r="O29" s="9">
         <v>4.9479627544026217</v>
       </c>
-      <c r="O29" s="9">
+      <c r="P29" s="9">
         <v>3.800222093309602</v>
       </c>
-      <c r="P29" s="22">
+      <c r="Q29" s="20">
         <v>2.1620575762215903</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
@@ -2182,44 +2251,47 @@
       <c r="D30" s="11">
         <v>90</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="9">
         <v>2.8095864818095313</v>
       </c>
-      <c r="F30" s="9">
+      <c r="G30" s="9">
         <v>5.3957827286710192</v>
       </c>
-      <c r="G30" s="9">
+      <c r="H30" s="9">
         <v>5.3503832384118741</v>
       </c>
-      <c r="H30" s="9">
+      <c r="I30" s="9">
         <v>13.344361598686229</v>
       </c>
-      <c r="I30" s="9">
+      <c r="J30" s="9">
         <v>22.923069610190264</v>
       </c>
-      <c r="J30" s="9">
+      <c r="K30" s="9">
         <v>41.961568091485923</v>
       </c>
-      <c r="K30" s="9">
+      <c r="L30" s="9">
         <v>26.467023145206021</v>
       </c>
-      <c r="L30" s="9">
+      <c r="M30" s="9">
         <v>21.79453973006644</v>
       </c>
-      <c r="M30" s="9">
+      <c r="N30" s="9">
         <v>10.467927838164099</v>
       </c>
-      <c r="N30" s="9">
+      <c r="O30" s="9">
         <v>4.9479627544026217</v>
       </c>
-      <c r="O30" s="9">
+      <c r="P30" s="9">
         <v>3.800222093309602</v>
       </c>
-      <c r="P30" s="22">
+      <c r="Q30" s="20">
         <v>2.1620575762215903</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -2232,44 +2304,23 @@
       <c r="D31" s="10">
         <v>30</v>
       </c>
-      <c r="E31" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F31" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G31" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H31" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I31" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J31" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K31" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L31" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M31" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N31" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O31" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P31" s="23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E31" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="19"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -2282,44 +2333,23 @@
       <c r="D32" s="10">
         <v>45</v>
       </c>
-      <c r="E32" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F32" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G32" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H32" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I32" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J32" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K32" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L32" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M32" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N32" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O32" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P32" s="23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E32" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="19"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -2332,44 +2362,23 @@
       <c r="D33" s="10">
         <v>60</v>
       </c>
-      <c r="E33" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F33" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G33" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H33" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I33" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J33" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K33" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L33" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M33" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N33" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O33" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P33" s="23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E33" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="19"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
@@ -2382,49 +2391,28 @@
       <c r="D34" s="14">
         <v>90</v>
       </c>
-      <c r="E34" s="15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F34" s="15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G34" s="15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H34" s="15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I34" s="15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J34" s="15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K34" s="15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L34" s="15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M34" s="15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N34" s="15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O34" s="15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P34" s="24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A35" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>14</v>
+      <c r="E34" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="19"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>4</v>
@@ -2432,7 +2420,9 @@
       <c r="D35" s="5">
         <v>0</v>
       </c>
-      <c r="E35" s="6"/>
+      <c r="E35" s="23" t="s">
+        <v>17</v>
+      </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
@@ -2443,14 +2433,15 @@
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
-      <c r="P35" s="21"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>14</v>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="19"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>5</v>
@@ -2458,49 +2449,52 @@
       <c r="D36" s="8">
         <v>30</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="9">
         <v>-9</v>
       </c>
-      <c r="F36" s="9">
+      <c r="G36" s="9">
         <v>-6.6170477249804103</v>
       </c>
-      <c r="G36" s="9">
+      <c r="H36" s="9">
         <v>-9.6318943203141671</v>
       </c>
-      <c r="H36" s="9">
+      <c r="I36" s="9">
         <v>-20.504919020166163</v>
       </c>
-      <c r="I36" s="9">
+      <c r="J36" s="9">
         <v>-37.052055722993167</v>
       </c>
-      <c r="J36" s="9">
+      <c r="K36" s="9">
         <v>-50.393218764536996</v>
       </c>
-      <c r="K36" s="9">
+      <c r="L36" s="9">
         <v>-37.133536639871863</v>
       </c>
-      <c r="L36" s="9">
+      <c r="M36" s="9">
         <v>-28.62643713532815</v>
       </c>
-      <c r="M36" s="9">
+      <c r="N36" s="9">
         <v>-18.740924816327567</v>
       </c>
-      <c r="N36" s="9">
+      <c r="O36" s="9">
         <v>-8.8486887805426235</v>
       </c>
-      <c r="O36" s="9">
+      <c r="P36" s="9">
         <v>-5.822850610852556</v>
       </c>
-      <c r="P36" s="22">
+      <c r="Q36" s="20">
         <v>-9</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A37" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>14</v>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>5</v>
@@ -2508,49 +2502,52 @@
       <c r="D37" s="10">
         <v>45</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="9">
         <v>-9</v>
       </c>
-      <c r="F37" s="9">
+      <c r="G37" s="9">
         <v>-6.6170477249804103</v>
       </c>
-      <c r="G37" s="9">
+      <c r="H37" s="9">
         <v>-9.6318943203141671</v>
       </c>
-      <c r="H37" s="9">
+      <c r="I37" s="9">
         <v>-20.504919020166163</v>
       </c>
-      <c r="I37" s="9">
+      <c r="J37" s="9">
         <v>-37.052055722993167</v>
       </c>
-      <c r="J37" s="9">
+      <c r="K37" s="9">
         <v>-50.393218764536996</v>
       </c>
-      <c r="K37" s="9">
+      <c r="L37" s="9">
         <v>-37.133536639871863</v>
       </c>
-      <c r="L37" s="9">
+      <c r="M37" s="9">
         <v>-28.62643713532815</v>
       </c>
-      <c r="M37" s="9">
+      <c r="N37" s="9">
         <v>-18.740924816327567</v>
       </c>
-      <c r="N37" s="9">
+      <c r="O37" s="9">
         <v>-8.8486887805426235</v>
       </c>
-      <c r="O37" s="9">
+      <c r="P37" s="9">
         <v>-5.822850610852556</v>
       </c>
-      <c r="P37" s="22">
+      <c r="Q37" s="20">
         <v>-9</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A38" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>14</v>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>5</v>
@@ -2558,49 +2555,52 @@
       <c r="D38" s="10">
         <v>60</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="9">
         <v>-9</v>
       </c>
-      <c r="F38" s="9">
+      <c r="G38" s="9">
         <v>-6.6170477249804103</v>
       </c>
-      <c r="G38" s="9">
+      <c r="H38" s="9">
         <v>-9.6318943203141671</v>
       </c>
-      <c r="H38" s="9">
+      <c r="I38" s="9">
         <v>-20.504919020166163</v>
       </c>
-      <c r="I38" s="9">
+      <c r="J38" s="9">
         <v>-37.052055722993167</v>
       </c>
-      <c r="J38" s="9">
+      <c r="K38" s="9">
         <v>-50.393218764536996</v>
       </c>
-      <c r="K38" s="9">
+      <c r="L38" s="9">
         <v>-37.133536639871863</v>
       </c>
-      <c r="L38" s="9">
+      <c r="M38" s="9">
         <v>-28.62643713532815</v>
       </c>
-      <c r="M38" s="9">
+      <c r="N38" s="9">
         <v>-18.740924816327567</v>
       </c>
-      <c r="N38" s="9">
+      <c r="O38" s="9">
         <v>-8.8486887805426235</v>
       </c>
-      <c r="O38" s="9">
+      <c r="P38" s="9">
         <v>-5.822850610852556</v>
       </c>
-      <c r="P38" s="22">
+      <c r="Q38" s="20">
         <v>-9</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A39" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>14</v>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>5</v>
@@ -2608,49 +2608,52 @@
       <c r="D39" s="11">
         <v>90</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="9">
         <v>-9</v>
       </c>
-      <c r="F39" s="9">
+      <c r="G39" s="9">
         <v>-6.6170477249804103</v>
       </c>
-      <c r="G39" s="9">
+      <c r="H39" s="9">
         <v>-9.6318943203141671</v>
       </c>
-      <c r="H39" s="9">
+      <c r="I39" s="9">
         <v>-20.504919020166163</v>
       </c>
-      <c r="I39" s="9">
+      <c r="J39" s="9">
         <v>-37.052055722993167</v>
       </c>
-      <c r="J39" s="9">
+      <c r="K39" s="9">
         <v>-50.393218764536996</v>
       </c>
-      <c r="K39" s="9">
+      <c r="L39" s="9">
         <v>-37.133536639871863</v>
       </c>
-      <c r="L39" s="9">
+      <c r="M39" s="9">
         <v>-28.62643713532815</v>
       </c>
-      <c r="M39" s="9">
+      <c r="N39" s="9">
         <v>-18.740924816327567</v>
       </c>
-      <c r="N39" s="9">
+      <c r="O39" s="9">
         <v>-8.8486887805426235</v>
       </c>
-      <c r="O39" s="9">
+      <c r="P39" s="9">
         <v>-5.822850610852556</v>
       </c>
-      <c r="P39" s="22">
+      <c r="Q39" s="20">
         <v>-9</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A40" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>14</v>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>6</v>
@@ -2658,49 +2661,52 @@
       <c r="D40" s="10">
         <v>30</v>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="13">
         <v>-3</v>
-      </c>
-      <c r="F40" s="13">
-        <v>-2</v>
       </c>
       <c r="G40" s="13">
         <v>-2</v>
       </c>
       <c r="H40" s="13">
+        <v>-2</v>
+      </c>
+      <c r="I40" s="13">
         <v>-16.559739399914424</v>
       </c>
-      <c r="I40" s="13">
+      <c r="J40" s="13">
         <v>-35.613505808711317</v>
       </c>
-      <c r="J40" s="13">
+      <c r="K40" s="13">
         <v>-49.189995404138642</v>
       </c>
-      <c r="K40" s="13">
+      <c r="L40" s="13">
         <v>-35.559920597120957</v>
       </c>
-      <c r="L40" s="13">
+      <c r="M40" s="13">
         <v>-25.727811350480433</v>
       </c>
-      <c r="M40" s="13">
+      <c r="N40" s="13">
         <v>-13.486163430438305</v>
       </c>
-      <c r="N40" s="13">
+      <c r="O40" s="13">
         <v>-1.6119621670828921</v>
       </c>
-      <c r="O40" s="13">
+      <c r="P40" s="13">
         <v>-3</v>
       </c>
-      <c r="P40" s="23">
+      <c r="Q40" s="21">
         <v>-3</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A41" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>14</v>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>6</v>
@@ -2708,49 +2714,52 @@
       <c r="D41" s="10">
         <v>45</v>
       </c>
-      <c r="E41" s="13">
+      <c r="E41" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="13">
         <v>-3</v>
-      </c>
-      <c r="F41" s="13">
-        <v>-2</v>
       </c>
       <c r="G41" s="13">
         <v>-2</v>
       </c>
       <c r="H41" s="13">
+        <v>-2</v>
+      </c>
+      <c r="I41" s="13">
         <v>-16.559739399914424</v>
       </c>
-      <c r="I41" s="13">
+      <c r="J41" s="13">
         <v>-35.613505808711317</v>
       </c>
-      <c r="J41" s="13">
+      <c r="K41" s="13">
         <v>-49.189995404138642</v>
       </c>
-      <c r="K41" s="13">
+      <c r="L41" s="13">
         <v>-35.559920597120957</v>
       </c>
-      <c r="L41" s="13">
+      <c r="M41" s="13">
         <v>-25.727811350480433</v>
       </c>
-      <c r="M41" s="13">
+      <c r="N41" s="13">
         <v>-13.486163430438305</v>
       </c>
-      <c r="N41" s="13">
+      <c r="O41" s="13">
         <v>-1.6119621670828921</v>
       </c>
-      <c r="O41" s="13">
+      <c r="P41" s="13">
         <v>-3</v>
       </c>
-      <c r="P41" s="23">
+      <c r="Q41" s="21">
         <v>-3</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A42" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>14</v>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>6</v>
@@ -2758,49 +2767,52 @@
       <c r="D42" s="10">
         <v>60</v>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="13">
         <v>-3</v>
-      </c>
-      <c r="F42" s="13">
-        <v>-2</v>
       </c>
       <c r="G42" s="13">
         <v>-2</v>
       </c>
       <c r="H42" s="13">
+        <v>-2</v>
+      </c>
+      <c r="I42" s="13">
         <v>-16.559739399914424</v>
       </c>
-      <c r="I42" s="13">
+      <c r="J42" s="13">
         <v>-35.613505808711317</v>
       </c>
-      <c r="J42" s="13">
+      <c r="K42" s="13">
         <v>-49.189995404138642</v>
       </c>
-      <c r="K42" s="13">
+      <c r="L42" s="13">
         <v>-35.559920597120957</v>
       </c>
-      <c r="L42" s="13">
+      <c r="M42" s="13">
         <v>-25.727811350480433</v>
       </c>
-      <c r="M42" s="13">
+      <c r="N42" s="13">
         <v>-13.486163430438305</v>
       </c>
-      <c r="N42" s="13">
+      <c r="O42" s="13">
         <v>-1.6119621670828921</v>
       </c>
-      <c r="O42" s="13">
+      <c r="P42" s="13">
         <v>-3</v>
       </c>
-      <c r="P42" s="23">
+      <c r="Q42" s="21">
         <v>-3</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A43" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>14</v>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>6</v>
@@ -2808,49 +2820,52 @@
       <c r="D43" s="10">
         <v>90</v>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="13">
         <v>-3</v>
-      </c>
-      <c r="F43" s="13">
-        <v>-2</v>
       </c>
       <c r="G43" s="13">
         <v>-2</v>
       </c>
       <c r="H43" s="13">
+        <v>-2</v>
+      </c>
+      <c r="I43" s="13">
         <v>-16.559739399914424</v>
       </c>
-      <c r="I43" s="13">
+      <c r="J43" s="13">
         <v>-35.613505808711317</v>
       </c>
-      <c r="J43" s="13">
+      <c r="K43" s="13">
         <v>-49.189995404138642</v>
       </c>
-      <c r="K43" s="13">
+      <c r="L43" s="13">
         <v>-35.559920597120957</v>
       </c>
-      <c r="L43" s="13">
+      <c r="M43" s="13">
         <v>-25.727811350480433</v>
       </c>
-      <c r="M43" s="13">
+      <c r="N43" s="13">
         <v>-13.486163430438305</v>
       </c>
-      <c r="N43" s="13">
+      <c r="O43" s="13">
         <v>-1.6119621670828921</v>
       </c>
-      <c r="O43" s="13">
+      <c r="P43" s="13">
         <v>-3</v>
       </c>
-      <c r="P43" s="23">
+      <c r="Q43" s="21">
         <v>-3</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A44" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>14</v>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>7</v>
@@ -2858,49 +2873,52 @@
       <c r="D44" s="8">
         <v>30</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="9">
         <v>-8</v>
       </c>
-      <c r="F44" s="9">
+      <c r="G44" s="9">
         <v>-7.9768643340104433</v>
       </c>
-      <c r="G44" s="9">
+      <c r="H44" s="9">
         <v>-11.026184940719666</v>
       </c>
-      <c r="H44" s="9">
+      <c r="I44" s="9">
         <v>-20.353582037131648</v>
       </c>
-      <c r="I44" s="9">
+      <c r="J44" s="9">
         <v>-34.261966601866632</v>
       </c>
-      <c r="J44" s="9">
+      <c r="K44" s="9">
         <v>-46.896998687623949</v>
       </c>
-      <c r="K44" s="9">
+      <c r="L44" s="9">
         <v>-34.782332599520672</v>
       </c>
-      <c r="L44" s="9">
+      <c r="M44" s="9">
         <v>-27.497399456860521</v>
       </c>
-      <c r="M44" s="9">
+      <c r="N44" s="9">
         <v>-18.998653501849354</v>
       </c>
-      <c r="N44" s="9">
+      <c r="O44" s="9">
         <v>-10.426598277506125</v>
       </c>
-      <c r="O44" s="9">
+      <c r="P44" s="9">
         <v>-6.8612486414018248</v>
       </c>
-      <c r="P44" s="22">
+      <c r="Q44" s="20">
         <v>-8</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A45" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>14</v>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>7</v>
@@ -2908,49 +2926,52 @@
       <c r="D45" s="10">
         <v>45</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="9">
         <v>-8</v>
       </c>
-      <c r="F45" s="9">
+      <c r="G45" s="9">
         <v>-7.9768643340104433</v>
       </c>
-      <c r="G45" s="9">
+      <c r="H45" s="9">
         <v>-11.026184940719666</v>
       </c>
-      <c r="H45" s="9">
+      <c r="I45" s="9">
         <v>-20.353582037131648</v>
       </c>
-      <c r="I45" s="9">
+      <c r="J45" s="9">
         <v>-34.261966601866632</v>
       </c>
-      <c r="J45" s="9">
+      <c r="K45" s="9">
         <v>-46.896998687623949</v>
       </c>
-      <c r="K45" s="9">
+      <c r="L45" s="9">
         <v>-34.782332599520672</v>
       </c>
-      <c r="L45" s="9">
+      <c r="M45" s="9">
         <v>-27.497399456860521</v>
       </c>
-      <c r="M45" s="9">
+      <c r="N45" s="9">
         <v>-18.998653501849354</v>
       </c>
-      <c r="N45" s="9">
+      <c r="O45" s="9">
         <v>-10.426598277506125</v>
       </c>
-      <c r="O45" s="9">
+      <c r="P45" s="9">
         <v>-6.8612486414018248</v>
       </c>
-      <c r="P45" s="22">
+      <c r="Q45" s="20">
         <v>-8</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A46" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>14</v>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>7</v>
@@ -2958,49 +2979,52 @@
       <c r="D46" s="10">
         <v>60</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="9">
         <v>-8</v>
       </c>
-      <c r="F46" s="9">
+      <c r="G46" s="9">
         <v>-7.9768643340104433</v>
       </c>
-      <c r="G46" s="9">
+      <c r="H46" s="9">
         <v>-11.026184940719666</v>
       </c>
-      <c r="H46" s="9">
+      <c r="I46" s="9">
         <v>-20.353582037131648</v>
       </c>
-      <c r="I46" s="9">
+      <c r="J46" s="9">
         <v>-34.261966601866632</v>
       </c>
-      <c r="J46" s="9">
+      <c r="K46" s="9">
         <v>-46.896998687623949</v>
       </c>
-      <c r="K46" s="9">
+      <c r="L46" s="9">
         <v>-34.782332599520672</v>
       </c>
-      <c r="L46" s="9">
+      <c r="M46" s="9">
         <v>-27.497399456860521</v>
       </c>
-      <c r="M46" s="9">
+      <c r="N46" s="9">
         <v>-18.998653501849354</v>
       </c>
-      <c r="N46" s="9">
+      <c r="O46" s="9">
         <v>-10.426598277506125</v>
       </c>
-      <c r="O46" s="9">
+      <c r="P46" s="9">
         <v>-6.8612486414018248</v>
       </c>
-      <c r="P46" s="22">
+      <c r="Q46" s="20">
         <v>-8</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A47" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>14</v>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>7</v>
@@ -3008,49 +3032,52 @@
       <c r="D47" s="11">
         <v>90</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="9">
         <v>-8</v>
       </c>
-      <c r="F47" s="9">
+      <c r="G47" s="9">
         <v>-7.9768643340104433</v>
       </c>
-      <c r="G47" s="9">
+      <c r="H47" s="9">
         <v>-11.026184940719666</v>
       </c>
-      <c r="H47" s="9">
+      <c r="I47" s="9">
         <v>-20.353582037131648</v>
       </c>
-      <c r="I47" s="9">
+      <c r="J47" s="9">
         <v>-34.261966601866632</v>
       </c>
-      <c r="J47" s="9">
+      <c r="K47" s="9">
         <v>-46.896998687623949</v>
       </c>
-      <c r="K47" s="9">
+      <c r="L47" s="9">
         <v>-34.782332599520672</v>
       </c>
-      <c r="L47" s="9">
+      <c r="M47" s="9">
         <v>-27.497399456860521</v>
       </c>
-      <c r="M47" s="9">
+      <c r="N47" s="9">
         <v>-18.998653501849354</v>
       </c>
-      <c r="N47" s="9">
+      <c r="O47" s="9">
         <v>-10.426598277506125</v>
       </c>
-      <c r="O47" s="9">
+      <c r="P47" s="9">
         <v>-6.8612486414018248</v>
       </c>
-      <c r="P47" s="22">
+      <c r="Q47" s="20">
         <v>-8</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A48" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>14</v>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>8</v>
@@ -3058,49 +3085,52 @@
       <c r="D48" s="10">
         <v>30</v>
       </c>
-      <c r="E48" s="13">
-        <v>0</v>
+      <c r="E48" s="23" t="s">
+        <v>17</v>
       </c>
       <c r="F48" s="13">
         <v>0</v>
       </c>
       <c r="G48" s="13">
+        <v>0</v>
+      </c>
+      <c r="H48" s="13">
         <v>-1.875217431783349</v>
       </c>
-      <c r="H48" s="13">
+      <c r="I48" s="13">
         <v>-12.875260224836191</v>
       </c>
-      <c r="I48" s="13">
+      <c r="J48" s="13">
         <v>-30.990256348700715</v>
       </c>
-      <c r="J48" s="13">
+      <c r="K48" s="13">
         <v>-42.605832810850927</v>
       </c>
-      <c r="K48" s="13">
+      <c r="L48" s="13">
         <v>-30.326034293392759</v>
       </c>
-      <c r="L48" s="13">
+      <c r="M48" s="13">
         <v>-20.818783268080612</v>
       </c>
-      <c r="M48" s="13">
+      <c r="N48" s="13">
         <v>-9.8942055498573538</v>
       </c>
-      <c r="N48" s="13">
-        <v>0</v>
-      </c>
       <c r="O48" s="13">
         <v>0</v>
       </c>
-      <c r="P48" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A49" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>14</v>
+      <c r="P48" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>8</v>
@@ -3108,49 +3138,52 @@
       <c r="D49" s="10">
         <v>45</v>
       </c>
-      <c r="E49" s="13">
-        <v>0</v>
+      <c r="E49" s="23" t="s">
+        <v>17</v>
       </c>
       <c r="F49" s="13">
         <v>0</v>
       </c>
       <c r="G49" s="13">
+        <v>0</v>
+      </c>
+      <c r="H49" s="13">
         <v>-1.875217431783349</v>
       </c>
-      <c r="H49" s="13">
+      <c r="I49" s="13">
         <v>-12.875260224836191</v>
       </c>
-      <c r="I49" s="13">
+      <c r="J49" s="13">
         <v>-30.990256348700715</v>
       </c>
-      <c r="J49" s="13">
+      <c r="K49" s="13">
         <v>-42.605832810850927</v>
       </c>
-      <c r="K49" s="13">
+      <c r="L49" s="13">
         <v>-30.326034293392759</v>
       </c>
-      <c r="L49" s="13">
+      <c r="M49" s="13">
         <v>-20.818783268080612</v>
       </c>
-      <c r="M49" s="13">
+      <c r="N49" s="13">
         <v>-9.8942055498573538</v>
       </c>
-      <c r="N49" s="13">
-        <v>0</v>
-      </c>
       <c r="O49" s="13">
         <v>0</v>
       </c>
-      <c r="P49" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A50" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>14</v>
+      <c r="P49" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>8</v>
@@ -3158,49 +3191,52 @@
       <c r="D50" s="10">
         <v>60</v>
       </c>
-      <c r="E50" s="13">
-        <v>0</v>
+      <c r="E50" s="23" t="s">
+        <v>17</v>
       </c>
       <c r="F50" s="13">
         <v>0</v>
       </c>
       <c r="G50" s="13">
+        <v>0</v>
+      </c>
+      <c r="H50" s="13">
         <v>-1.875217431783349</v>
       </c>
-      <c r="H50" s="13">
+      <c r="I50" s="13">
         <v>-12.875260224836191</v>
       </c>
-      <c r="I50" s="13">
+      <c r="J50" s="13">
         <v>-30.990256348700715</v>
       </c>
-      <c r="J50" s="13">
+      <c r="K50" s="13">
         <v>-42.605832810850927</v>
       </c>
-      <c r="K50" s="13">
+      <c r="L50" s="13">
         <v>-30.326034293392759</v>
       </c>
-      <c r="L50" s="13">
+      <c r="M50" s="13">
         <v>-20.818783268080612</v>
       </c>
-      <c r="M50" s="13">
+      <c r="N50" s="13">
         <v>-9.8942055498573538</v>
       </c>
-      <c r="N50" s="13">
-        <v>0</v>
-      </c>
       <c r="O50" s="13">
         <v>0</v>
       </c>
-      <c r="P50" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A51" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>14</v>
+      <c r="P50" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>8</v>
@@ -3208,49 +3244,52 @@
       <c r="D51" s="10">
         <v>90</v>
       </c>
-      <c r="E51" s="13">
-        <v>0</v>
+      <c r="E51" s="23" t="s">
+        <v>17</v>
       </c>
       <c r="F51" s="13">
         <v>0</v>
       </c>
       <c r="G51" s="13">
+        <v>0</v>
+      </c>
+      <c r="H51" s="13">
         <v>-1.875217431783349</v>
       </c>
-      <c r="H51" s="13">
+      <c r="I51" s="13">
         <v>-12.875260224836191</v>
       </c>
-      <c r="I51" s="13">
+      <c r="J51" s="13">
         <v>-30.990256348700715</v>
       </c>
-      <c r="J51" s="13">
+      <c r="K51" s="13">
         <v>-42.605832810850927</v>
       </c>
-      <c r="K51" s="13">
+      <c r="L51" s="13">
         <v>-30.326034293392759</v>
       </c>
-      <c r="L51" s="13">
+      <c r="M51" s="13">
         <v>-20.818783268080612</v>
       </c>
-      <c r="M51" s="13">
+      <c r="N51" s="13">
         <v>-9.8942055498573538</v>
       </c>
-      <c r="N51" s="13">
-        <v>0</v>
-      </c>
       <c r="O51" s="13">
         <v>0</v>
       </c>
-      <c r="P51" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A52" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>14</v>
+      <c r="P51" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>9</v>
@@ -3258,49 +3297,52 @@
       <c r="D52" s="8">
         <v>30</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="9">
         <v>-3.3947316605246529</v>
       </c>
-      <c r="F52" s="9">
+      <c r="G52" s="9">
         <v>-5.208948944220281</v>
       </c>
-      <c r="G52" s="9">
+      <c r="H52" s="9">
         <v>-8.4128661757337699</v>
       </c>
-      <c r="H52" s="9">
+      <c r="I52" s="9">
         <v>-16.909007889752854</v>
       </c>
-      <c r="I52" s="9">
+      <c r="J52" s="9">
         <v>-29.681709065399108</v>
       </c>
-      <c r="J52" s="9">
+      <c r="K52" s="9">
         <v>-42.909291800843178</v>
       </c>
-      <c r="K52" s="9">
+      <c r="L52" s="9">
         <v>-31.27112548948088</v>
       </c>
-      <c r="L52" s="9">
+      <c r="M52" s="9">
         <v>-23.64113992070569</v>
       </c>
-      <c r="M52" s="9">
+      <c r="N52" s="9">
         <v>-14.998870556645389</v>
       </c>
-      <c r="N52" s="9">
+      <c r="O52" s="9">
         <v>-7.2883533641957605</v>
       </c>
-      <c r="O52" s="9">
+      <c r="P52" s="9">
         <v>-4.2539921986875511</v>
       </c>
-      <c r="P52" s="22">
+      <c r="Q52" s="20">
         <v>-3.71605861389396</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A53" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>14</v>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>9</v>
@@ -3308,49 +3350,52 @@
       <c r="D53" s="10">
         <v>45</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="9">
         <v>-3.3947316605246529</v>
       </c>
-      <c r="F53" s="9">
+      <c r="G53" s="9">
         <v>-5.208948944220281</v>
       </c>
-      <c r="G53" s="9">
+      <c r="H53" s="9">
         <v>-8.4128661757337699</v>
       </c>
-      <c r="H53" s="9">
+      <c r="I53" s="9">
         <v>-16.909007889752854</v>
       </c>
-      <c r="I53" s="9">
+      <c r="J53" s="9">
         <v>-29.681709065399108</v>
       </c>
-      <c r="J53" s="9">
+      <c r="K53" s="9">
         <v>-42.909291800843178</v>
       </c>
-      <c r="K53" s="9">
+      <c r="L53" s="9">
         <v>-31.27112548948088</v>
       </c>
-      <c r="L53" s="9">
+      <c r="M53" s="9">
         <v>-23.64113992070569</v>
       </c>
-      <c r="M53" s="9">
+      <c r="N53" s="9">
         <v>-14.998870556645389</v>
       </c>
-      <c r="N53" s="9">
+      <c r="O53" s="9">
         <v>-7.2883533641957605</v>
       </c>
-      <c r="O53" s="9">
+      <c r="P53" s="9">
         <v>-4.2539921986875511</v>
       </c>
-      <c r="P53" s="22">
+      <c r="Q53" s="20">
         <v>-3.71605861389396</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A54" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B54" s="17" t="s">
-        <v>14</v>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>9</v>
@@ -3358,49 +3403,52 @@
       <c r="D54" s="10">
         <v>60</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="9">
         <v>-3.3947316605246529</v>
       </c>
-      <c r="F54" s="9">
+      <c r="G54" s="9">
         <v>-5.208948944220281</v>
       </c>
-      <c r="G54" s="9">
+      <c r="H54" s="9">
         <v>-8.4128661757337699</v>
       </c>
-      <c r="H54" s="9">
+      <c r="I54" s="9">
         <v>-16.909007889752854</v>
       </c>
-      <c r="I54" s="9">
+      <c r="J54" s="9">
         <v>-29.681709065399108</v>
       </c>
-      <c r="J54" s="9">
+      <c r="K54" s="9">
         <v>-42.909291800843178</v>
       </c>
-      <c r="K54" s="9">
+      <c r="L54" s="9">
         <v>-31.27112548948088</v>
       </c>
-      <c r="L54" s="9">
+      <c r="M54" s="9">
         <v>-23.64113992070569</v>
       </c>
-      <c r="M54" s="9">
+      <c r="N54" s="9">
         <v>-14.998870556645389</v>
       </c>
-      <c r="N54" s="9">
+      <c r="O54" s="9">
         <v>-7.2883533641957605</v>
       </c>
-      <c r="O54" s="9">
+      <c r="P54" s="9">
         <v>-4.2539921986875511</v>
       </c>
-      <c r="P54" s="22">
+      <c r="Q54" s="20">
         <v>-3.71605861389396</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A55" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>14</v>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>9</v>
@@ -3408,49 +3456,52 @@
       <c r="D55" s="11">
         <v>90</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="9">
         <v>-3.3947316605246529</v>
       </c>
-      <c r="F55" s="9">
+      <c r="G55" s="9">
         <v>-5.208948944220281</v>
       </c>
-      <c r="G55" s="9">
+      <c r="H55" s="9">
         <v>-8.4128661757337699</v>
       </c>
-      <c r="H55" s="9">
+      <c r="I55" s="9">
         <v>-16.909007889752854</v>
       </c>
-      <c r="I55" s="9">
+      <c r="J55" s="9">
         <v>-29.681709065399108</v>
       </c>
-      <c r="J55" s="9">
+      <c r="K55" s="9">
         <v>-42.909291800843178</v>
       </c>
-      <c r="K55" s="9">
+      <c r="L55" s="9">
         <v>-31.27112548948088</v>
       </c>
-      <c r="L55" s="9">
+      <c r="M55" s="9">
         <v>-23.64113992070569</v>
       </c>
-      <c r="M55" s="9">
+      <c r="N55" s="9">
         <v>-14.998870556645389</v>
       </c>
-      <c r="N55" s="9">
+      <c r="O55" s="9">
         <v>-7.2883533641957605</v>
       </c>
-      <c r="O55" s="9">
+      <c r="P55" s="9">
         <v>-4.2539921986875511</v>
       </c>
-      <c r="P55" s="22">
+      <c r="Q55" s="20">
         <v>-3.71605861389396</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A56" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B56" s="17" t="s">
-        <v>14</v>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>10</v>
@@ -3458,49 +3509,52 @@
       <c r="D56" s="10">
         <v>30</v>
       </c>
-      <c r="E56" s="13">
+      <c r="E56" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="13">
         <v>-2.4452284673671936</v>
       </c>
-      <c r="F56" s="13">
+      <c r="G56" s="13">
         <v>-3.5952035163764533</v>
       </c>
-      <c r="G56" s="13">
+      <c r="H56" s="13">
         <v>-6.7132295369271953</v>
       </c>
-      <c r="H56" s="13">
+      <c r="I56" s="13">
         <v>-14.365682381935377</v>
       </c>
-      <c r="I56" s="13">
+      <c r="J56" s="13">
         <v>-26.244443329121527</v>
       </c>
-      <c r="J56" s="13">
+      <c r="K56" s="13">
         <v>-39.625346752267028</v>
       </c>
-      <c r="K56" s="13">
+      <c r="L56" s="13">
         <v>-28.545169170033169</v>
       </c>
-      <c r="L56" s="13">
+      <c r="M56" s="13">
         <v>-20.572476279148127</v>
       </c>
-      <c r="M56" s="13">
+      <c r="N56" s="13">
         <v>-12.217432126932511</v>
       </c>
-      <c r="N56" s="13">
+      <c r="O56" s="13">
         <v>-5.4112134797138225</v>
       </c>
-      <c r="O56" s="13">
+      <c r="P56" s="13">
         <v>-2.9172623050390105</v>
       </c>
-      <c r="P56" s="23">
+      <c r="Q56" s="21">
         <v>-2.7754925504922743</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A57" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B57" s="17" t="s">
-        <v>14</v>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>10</v>
@@ -3508,49 +3562,52 @@
       <c r="D57" s="10">
         <v>45</v>
       </c>
-      <c r="E57" s="13">
+      <c r="E57" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="13">
         <v>-2.4452284673671936</v>
       </c>
-      <c r="F57" s="13">
+      <c r="G57" s="13">
         <v>-3.5952035163764533</v>
       </c>
-      <c r="G57" s="13">
+      <c r="H57" s="13">
         <v>-6.7132295369271953</v>
       </c>
-      <c r="H57" s="13">
+      <c r="I57" s="13">
         <v>-14.365682381935377</v>
       </c>
-      <c r="I57" s="13">
+      <c r="J57" s="13">
         <v>-26.244443329121527</v>
       </c>
-      <c r="J57" s="13">
+      <c r="K57" s="13">
         <v>-39.625346752267028</v>
       </c>
-      <c r="K57" s="13">
+      <c r="L57" s="13">
         <v>-28.545169170033169</v>
       </c>
-      <c r="L57" s="13">
+      <c r="M57" s="13">
         <v>-20.572476279148127</v>
       </c>
-      <c r="M57" s="13">
+      <c r="N57" s="13">
         <v>-12.217432126932511</v>
       </c>
-      <c r="N57" s="13">
+      <c r="O57" s="13">
         <v>-5.4112134797138225</v>
       </c>
-      <c r="O57" s="13">
+      <c r="P57" s="13">
         <v>-2.9172623050390105</v>
       </c>
-      <c r="P57" s="23">
+      <c r="Q57" s="21">
         <v>-2.7754925504922743</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B58" s="17" t="s">
-        <v>14</v>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>10</v>
@@ -3558,49 +3615,52 @@
       <c r="D58" s="10">
         <v>60</v>
       </c>
-      <c r="E58" s="13">
+      <c r="E58" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="13">
         <v>-2.4452284673671936</v>
       </c>
-      <c r="F58" s="13">
+      <c r="G58" s="13">
         <v>-3.5952035163764533</v>
       </c>
-      <c r="G58" s="13">
+      <c r="H58" s="13">
         <v>-6.7132295369271953</v>
       </c>
-      <c r="H58" s="13">
+      <c r="I58" s="13">
         <v>-14.365682381935377</v>
       </c>
-      <c r="I58" s="13">
+      <c r="J58" s="13">
         <v>-26.244443329121527</v>
       </c>
-      <c r="J58" s="13">
+      <c r="K58" s="13">
         <v>-39.625346752267028</v>
       </c>
-      <c r="K58" s="13">
+      <c r="L58" s="13">
         <v>-28.545169170033169</v>
       </c>
-      <c r="L58" s="13">
+      <c r="M58" s="13">
         <v>-20.572476279148127</v>
       </c>
-      <c r="M58" s="13">
+      <c r="N58" s="13">
         <v>-12.217432126932511</v>
       </c>
-      <c r="N58" s="13">
+      <c r="O58" s="13">
         <v>-5.4112134797138225</v>
       </c>
-      <c r="O58" s="13">
+      <c r="P58" s="13">
         <v>-2.9172623050390105</v>
       </c>
-      <c r="P58" s="23">
+      <c r="Q58" s="21">
         <v>-2.7754925504922743</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A59" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B59" s="17" t="s">
-        <v>14</v>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>10</v>
@@ -3608,49 +3668,52 @@
       <c r="D59" s="10">
         <v>90</v>
       </c>
-      <c r="E59" s="13">
+      <c r="E59" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="13">
         <v>-2.4452284673671936</v>
       </c>
-      <c r="F59" s="13">
+      <c r="G59" s="13">
         <v>-3.5952035163764533</v>
       </c>
-      <c r="G59" s="13">
+      <c r="H59" s="13">
         <v>-6.7132295369271953</v>
       </c>
-      <c r="H59" s="13">
+      <c r="I59" s="13">
         <v>-14.365682381935377</v>
       </c>
-      <c r="I59" s="13">
+      <c r="J59" s="13">
         <v>-26.244443329121527</v>
       </c>
-      <c r="J59" s="13">
+      <c r="K59" s="13">
         <v>-39.625346752267028</v>
       </c>
-      <c r="K59" s="13">
+      <c r="L59" s="13">
         <v>-28.545169170033169</v>
       </c>
-      <c r="L59" s="13">
+      <c r="M59" s="13">
         <v>-20.572476279148127</v>
       </c>
-      <c r="M59" s="13">
+      <c r="N59" s="13">
         <v>-12.217432126932511</v>
       </c>
-      <c r="N59" s="13">
+      <c r="O59" s="13">
         <v>-5.4112134797138225</v>
       </c>
-      <c r="O59" s="13">
+      <c r="P59" s="13">
         <v>-2.9172623050390105</v>
       </c>
-      <c r="P59" s="23">
+      <c r="Q59" s="21">
         <v>-2.7754925504922743</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A60" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B60" s="17" t="s">
-        <v>14</v>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>11</v>
@@ -3658,8 +3721,8 @@
       <c r="D60" s="8">
         <v>30</v>
       </c>
-      <c r="E60" s="9">
-        <v>0</v>
+      <c r="E60" s="23" t="s">
+        <v>17</v>
       </c>
       <c r="F60" s="9">
         <v>0</v>
@@ -3674,14 +3737,14 @@
         <v>0</v>
       </c>
       <c r="J60" s="9">
+        <v>0</v>
+      </c>
+      <c r="K60" s="9">
         <v>-1.750047082419488E-2</v>
       </c>
-      <c r="K60" s="9">
+      <c r="L60" s="9">
         <v>-2.5944963323454747E-2</v>
       </c>
-      <c r="L60" s="9">
-        <v>0</v>
-      </c>
       <c r="M60" s="9">
         <v>0</v>
       </c>
@@ -3691,16 +3754,19 @@
       <c r="O60" s="9">
         <v>0</v>
       </c>
-      <c r="P60" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A61" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B61" s="17" t="s">
-        <v>14</v>
+      <c r="P60" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>11</v>
@@ -3708,8 +3774,8 @@
       <c r="D61" s="10">
         <v>45</v>
       </c>
-      <c r="E61" s="9">
-        <v>0</v>
+      <c r="E61" s="23" t="s">
+        <v>17</v>
       </c>
       <c r="F61" s="9">
         <v>0</v>
@@ -3724,14 +3790,14 @@
         <v>0</v>
       </c>
       <c r="J61" s="9">
+        <v>0</v>
+      </c>
+      <c r="K61" s="9">
         <v>-1.750047082419488E-2</v>
       </c>
-      <c r="K61" s="9">
+      <c r="L61" s="9">
         <v>-2.5944963323454747E-2</v>
       </c>
-      <c r="L61" s="9">
-        <v>0</v>
-      </c>
       <c r="M61" s="9">
         <v>0</v>
       </c>
@@ -3741,16 +3807,19 @@
       <c r="O61" s="9">
         <v>0</v>
       </c>
-      <c r="P61" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A62" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B62" s="17" t="s">
-        <v>14</v>
+      <c r="P61" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>11</v>
@@ -3758,8 +3827,8 @@
       <c r="D62" s="10">
         <v>60</v>
       </c>
-      <c r="E62" s="9">
-        <v>0</v>
+      <c r="E62" s="23" t="s">
+        <v>17</v>
       </c>
       <c r="F62" s="9">
         <v>0</v>
@@ -3774,14 +3843,14 @@
         <v>0</v>
       </c>
       <c r="J62" s="9">
+        <v>0</v>
+      </c>
+      <c r="K62" s="9">
         <v>-1.750047082419488E-2</v>
       </c>
-      <c r="K62" s="9">
+      <c r="L62" s="9">
         <v>-2.5944963323454747E-2</v>
       </c>
-      <c r="L62" s="9">
-        <v>0</v>
-      </c>
       <c r="M62" s="9">
         <v>0</v>
       </c>
@@ -3791,16 +3860,19 @@
       <c r="O62" s="9">
         <v>0</v>
       </c>
-      <c r="P62" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A63" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>14</v>
+      <c r="P62" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>11</v>
@@ -3808,8 +3880,8 @@
       <c r="D63" s="11">
         <v>90</v>
       </c>
-      <c r="E63" s="9">
-        <v>0</v>
+      <c r="E63" s="23" t="s">
+        <v>17</v>
       </c>
       <c r="F63" s="9">
         <v>0</v>
@@ -3824,14 +3896,14 @@
         <v>0</v>
       </c>
       <c r="J63" s="9">
+        <v>0</v>
+      </c>
+      <c r="K63" s="9">
         <v>-1.750047082419488E-2</v>
       </c>
-      <c r="K63" s="9">
+      <c r="L63" s="9">
         <v>-2.5944963323454747E-2</v>
       </c>
-      <c r="L63" s="9">
-        <v>0</v>
-      </c>
       <c r="M63" s="9">
         <v>0</v>
       </c>
@@ -3841,16 +3913,19 @@
       <c r="O63" s="9">
         <v>0</v>
       </c>
-      <c r="P63" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A64" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B64" s="17" t="s">
-        <v>14</v>
+      <c r="P63" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>12</v>
@@ -3858,49 +3933,52 @@
       <c r="D64" s="10">
         <v>30</v>
       </c>
-      <c r="E64" s="13">
+      <c r="E64" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" s="13">
         <v>-1.852331431511681</v>
       </c>
-      <c r="F64" s="13">
+      <c r="G64" s="13">
         <v>-2.563664871724697</v>
       </c>
-      <c r="G64" s="13">
+      <c r="H64" s="13">
         <v>-5.3838630592399292</v>
       </c>
-      <c r="H64" s="13">
+      <c r="I64" s="13">
         <v>-11.260206910951243</v>
       </c>
-      <c r="I64" s="13">
+      <c r="J64" s="13">
         <v>-20.182777012314467</v>
       </c>
-      <c r="J64" s="13">
+      <c r="K64" s="13">
         <v>-30.751268446444886</v>
       </c>
-      <c r="K64" s="13">
+      <c r="L64" s="13">
         <v>-22.466056987094468</v>
       </c>
-      <c r="L64" s="13">
+      <c r="M64" s="13">
         <v>-15.923351824848988</v>
       </c>
-      <c r="M64" s="13">
+      <c r="N64" s="13">
         <v>-9.5224975044351616</v>
       </c>
-      <c r="N64" s="13">
+      <c r="O64" s="13">
         <v>-4.1585595677753062</v>
       </c>
-      <c r="O64" s="13">
+      <c r="P64" s="13">
         <v>-2.0936995818332229</v>
       </c>
-      <c r="P64" s="23">
+      <c r="Q64" s="21">
         <v>-2.2034449655722455</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A65" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B65" s="17" t="s">
-        <v>14</v>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>12</v>
@@ -3908,49 +3986,52 @@
       <c r="D65" s="10">
         <v>45</v>
       </c>
-      <c r="E65" s="13">
+      <c r="E65" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="13">
         <v>-1.852331431511681</v>
       </c>
-      <c r="F65" s="13">
+      <c r="G65" s="13">
         <v>-2.563664871724697</v>
       </c>
-      <c r="G65" s="13">
+      <c r="H65" s="13">
         <v>-5.3838630592399292</v>
       </c>
-      <c r="H65" s="13">
+      <c r="I65" s="13">
         <v>-11.260206910951243</v>
       </c>
-      <c r="I65" s="13">
+      <c r="J65" s="13">
         <v>-20.182777012314467</v>
       </c>
-      <c r="J65" s="13">
+      <c r="K65" s="13">
         <v>-30.751268446444886</v>
       </c>
-      <c r="K65" s="13">
+      <c r="L65" s="13">
         <v>-22.466056987094468</v>
       </c>
-      <c r="L65" s="13">
+      <c r="M65" s="13">
         <v>-15.923351824848988</v>
       </c>
-      <c r="M65" s="13">
+      <c r="N65" s="13">
         <v>-9.5224975044351616</v>
       </c>
-      <c r="N65" s="13">
+      <c r="O65" s="13">
         <v>-4.1585595677753062</v>
       </c>
-      <c r="O65" s="13">
+      <c r="P65" s="13">
         <v>-2.0936995818332229</v>
       </c>
-      <c r="P65" s="23">
+      <c r="Q65" s="21">
         <v>-2.2034449655722455</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A66" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B66" s="17" t="s">
-        <v>14</v>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>12</v>
@@ -3958,49 +4039,52 @@
       <c r="D66" s="10">
         <v>60</v>
       </c>
-      <c r="E66" s="13">
+      <c r="E66" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" s="13">
         <v>-1.852331431511681</v>
       </c>
-      <c r="F66" s="13">
+      <c r="G66" s="13">
         <v>-2.563664871724697</v>
       </c>
-      <c r="G66" s="13">
+      <c r="H66" s="13">
         <v>-5.3838630592399292</v>
       </c>
-      <c r="H66" s="13">
+      <c r="I66" s="13">
         <v>-11.260206910951243</v>
       </c>
-      <c r="I66" s="13">
+      <c r="J66" s="13">
         <v>-20.182777012314467</v>
       </c>
-      <c r="J66" s="13">
+      <c r="K66" s="13">
         <v>-30.751268446444886</v>
       </c>
-      <c r="K66" s="13">
+      <c r="L66" s="13">
         <v>-22.466056987094468</v>
       </c>
-      <c r="L66" s="13">
+      <c r="M66" s="13">
         <v>-15.923351824848988</v>
       </c>
-      <c r="M66" s="13">
+      <c r="N66" s="13">
         <v>-9.5224975044351616</v>
       </c>
-      <c r="N66" s="13">
+      <c r="O66" s="13">
         <v>-4.1585595677753062</v>
       </c>
-      <c r="O66" s="13">
+      <c r="P66" s="13">
         <v>-2.0936995818332229</v>
       </c>
-      <c r="P66" s="23">
+      <c r="Q66" s="21">
         <v>-2.2034449655722455</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B67" s="17" t="s">
-        <v>14</v>
+    <row r="67" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>12</v>
@@ -4008,47 +4092,50 @@
       <c r="D67" s="14">
         <v>90</v>
       </c>
-      <c r="E67" s="15">
+      <c r="E67" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="15">
         <v>-1.852331431511681</v>
       </c>
-      <c r="F67" s="15">
+      <c r="G67" s="15">
         <v>-2.563664871724697</v>
       </c>
-      <c r="G67" s="15">
+      <c r="H67" s="15">
         <v>-5.3838630592399292</v>
       </c>
-      <c r="H67" s="15">
+      <c r="I67" s="15">
         <v>-11.260206910951243</v>
       </c>
-      <c r="I67" s="15">
+      <c r="J67" s="15">
         <v>-20.182777012314467</v>
       </c>
-      <c r="J67" s="15">
+      <c r="K67" s="15">
         <v>-30.751268446444886</v>
       </c>
-      <c r="K67" s="15">
+      <c r="L67" s="15">
         <v>-22.466056987094468</v>
       </c>
-      <c r="L67" s="15">
+      <c r="M67" s="15">
         <v>-15.923351824848988</v>
       </c>
-      <c r="M67" s="15">
+      <c r="N67" s="15">
         <v>-9.5224975044351616</v>
       </c>
-      <c r="N67" s="15">
+      <c r="O67" s="15">
         <v>-4.1585595677753062</v>
       </c>
-      <c r="O67" s="15">
+      <c r="P67" s="15">
         <v>-2.0936995818332229</v>
       </c>
-      <c r="P67" s="24">
+      <c r="Q67" s="22">
         <v>-2.2034449655722455</v>
       </c>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange password="DFD7" sqref="E24:P26 E2:P6 E19:P19" name="범위1_61_1_1"/>
-    <protectedRange password="DFD7" sqref="E57:P59 E35:P39 E52:P52" name="범위1_61_1"/>
+    <protectedRange password="DFD7" sqref="F24:Q26 F2:Q6 F19:Q19 F31:Q34" name="범위1_61_1_1"/>
+    <protectedRange password="DFD7" sqref="F57:Q59 F35:Q39 F52:Q52" name="범위1_61_1"/>
   </protectedRanges>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
